--- a/data/rules.xlsx
+++ b/data/rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0569FAA2-1CF7-3A4F-A013-9E15D4E718AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F70D93-FA37-334B-BB75-633BEB94EF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="29920" windowHeight="14180" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -9917,10 +9917,10 @@
     <t>a-ablaut not in Bäl, Pāś, läg and verbs with “ä + liquid + stop” if the morpheme (not Ipf/Prt) after causativity starts with z or vowel except ä</t>
   </si>
   <si>
-    <t>0~Morpheme~BAH2;-1~Pattern~[{_long}$|äy$]</t>
-  </si>
-  <si>
-    <t>BAH2 drops after long vowels and äy</t>
+    <t>BAH2 drops after long vowels and glides</t>
+  </si>
+  <si>
+    <t>0~Morpheme~BAH2;-1~Pattern~[{_long}$|w$|y$|v$]</t>
   </si>
 </sst>
 </file>
@@ -16130,7 +16130,7 @@
         <v>2192</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="D274" s="6"/>
       <c r="E274" s="6" t="s">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="F274" s="6"/>
       <c r="G274" s="6" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="H274" s="6"/>
     </row>

--- a/data/rules.xlsx
+++ b/data/rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3EA407-513F-794C-BFD5-AAA9D7B79B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991AAA6B-4AF3-1840-ABC2-AF66397026C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="3880" windowWidth="29920" windowHeight="14180" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>

--- a/data/rules.xlsx
+++ b/data/rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0116B5D5-DD7D-C54A-8037-C88DD925B2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92194A26-15B0-D84C-BA86-6287A037714F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3620" windowWidth="29920" windowHeight="14180" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
+    <workbookView xWindow="0" yWindow="7860" windowWidth="29920" windowHeight="14180" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="3" r:id="rId1"/>
@@ -9730,9 +9730,6 @@
   </si>
   <si>
     <t>BAH2 drops after long vowels and glides</t>
-  </si>
-  <si>
-    <t>0~Morpheme~BAH2;-1~Pattern~[{_long}$|w$|y$|v$]</t>
   </si>
   <si>
     <t>0~Before~n$|[{_long}]$|y$|v$|w$|s`$|nt$</t>
@@ -9892,6 +9889,9 @@
   </si>
   <si>
     <t>0~Morpheme~bäl,säl,pälzk,läṅk;2~Morpheme~REL3,INAN4,PREF</t>
+  </si>
+  <si>
+    <t>0~Morpheme~BAH2;-1~Pattern~[{_long}wyv]$</t>
   </si>
 </sst>
 </file>
@@ -16040,7 +16040,7 @@
         <v>2172</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>2896</v>
+        <v>2907</v>
       </c>
       <c r="D271" s="6"/>
       <c r="E271" s="6" t="s">
@@ -27494,7 +27494,7 @@
         <v>355</v>
       </c>
       <c r="D329" s="6" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="E329" s="6" t="s">
         <v>356</v>
@@ -29953,7 +29953,7 @@
         <v>2262</v>
       </c>
       <c r="C446" s="20" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="D446" s="20"/>
       <c r="E446" s="20" t="s">
@@ -29961,7 +29961,7 @@
       </c>
       <c r="F446" s="20"/>
       <c r="G446" s="20" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="H446" s="20"/>
     </row>
@@ -30702,14 +30702,14 @@
         <v>1005</v>
       </c>
       <c r="D482" s="16" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="E482" s="16" t="s">
         <v>211</v>
       </c>
       <c r="F482" s="16"/>
       <c r="G482" s="16" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="H482" s="16"/>
     </row>
@@ -30724,14 +30724,14 @@
         <v>627</v>
       </c>
       <c r="D483" s="16" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="E483" s="16" t="s">
         <v>628</v>
       </c>
       <c r="F483" s="16"/>
       <c r="G483" s="16" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="H483" s="16"/>
     </row>
@@ -30786,14 +30786,14 @@
         <v>1045</v>
       </c>
       <c r="D486" s="16" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="E486" s="16" t="s">
         <v>629</v>
       </c>
       <c r="F486" s="16"/>
       <c r="G486" s="16" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="H486" s="16"/>
     </row>
@@ -32031,18 +32031,18 @@
         <v>2281</v>
       </c>
       <c r="C545" s="6" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="D545" s="6"/>
       <c r="E545" s="6" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="F545" s="6"/>
       <c r="G545" s="6" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="H545" s="6" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.2">

--- a/data/rules.xlsx
+++ b/data/rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92194A26-15B0-D84C-BA86-6287A037714F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A9DE12-96F1-6B4E-B1E1-6C124908B340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="7860" windowWidth="29920" windowHeight="14180" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
+    <workbookView xWindow="0" yWindow="7680" windowWidth="29920" windowHeight="14180" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="3" r:id="rId1"/>
